--- a/BASE INTERNA.xlsx
+++ b/BASE INTERNA.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c055483\CEMIG\EI ET - Equipamentos - Documentos\TRAMITAÇÃO DE DOCUMENTOS\SCRIPT PYTHON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cemigbr.sharepoint.com/sites/eoet_equipamentos/Documentos Compartilhados/TRAMITAÇÃO DE DOCUMENTOS/SCRIPT PYTHON/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C294E3-B17F-4F70-BCBC-D5136A7396F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="284" documentId="8_{71FA6A9E-4B71-4B0B-AE43-8B20072134D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04CA4233-D7DD-44E2-BFE6-42DFE2472EF7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B330CE1A-85B8-4702-A854-85C1BDD9E2C6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B330CE1A-85B8-4702-A854-85C1BDD9E2C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$W$1:$W$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$Y$1:$Y$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="210">
   <si>
     <t>SUBESTACAO</t>
   </si>
@@ -218,15 +218,6 @@
     <t>CONTRATADA</t>
   </si>
   <si>
-    <t>CTRN</t>
-  </si>
-  <si>
-    <t>CYMI</t>
-  </si>
-  <si>
-    <t>MPE</t>
-  </si>
-  <si>
     <t>VISION</t>
   </si>
   <si>
@@ -248,18 +239,6 @@
     <t>WEG_CONTRATOS</t>
   </si>
   <si>
-    <t>4630003373</t>
-  </si>
-  <si>
-    <t>4680008098</t>
-  </si>
-  <si>
-    <t>4680008099</t>
-  </si>
-  <si>
-    <t>4680008100</t>
-  </si>
-  <si>
     <t>BRASIL REAL_EMPREENDIMENTOS</t>
   </si>
   <si>
@@ -299,9 +278,6 @@
     <t>WEG_RESPONSAVEIS</t>
   </si>
   <si>
-    <t>VITÓRIA SANTOS CÂNDIDO</t>
-  </si>
-  <si>
     <t>AGRUPAMENTO</t>
   </si>
   <si>
@@ -314,9 +290,6 @@
     <t>LINHAS DE TRANSMISSÃO - LT</t>
   </si>
   <si>
-    <t>BRASIL REAL</t>
-  </si>
-  <si>
     <t>EQP_SUBAGRUPAMENTO</t>
   </si>
   <si>
@@ -428,12 +401,6 @@
     <t>RODRIGO SERPA FERREIRA PASSOS</t>
   </si>
   <si>
-    <t>WEG</t>
-  </si>
-  <si>
-    <t>TECNOVA</t>
-  </si>
-  <si>
     <t>4680008320</t>
   </si>
   <si>
@@ -455,30 +422,6 @@
     <t>CARLA PINHEIRO</t>
   </si>
   <si>
-    <t>CESAR CUSTÓDIO</t>
-  </si>
-  <si>
-    <t>NIKOLAS LEMOS BAHIA DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>JEAN ALMEIDA FIRMINO</t>
-  </si>
-  <si>
-    <t>LAURA BARBOSA GUERRA</t>
-  </si>
-  <si>
-    <t>AMANDA FELIPETTO ALVES PEREIRA</t>
-  </si>
-  <si>
-    <t>SUSI WILMA SCHNEIDER</t>
-  </si>
-  <si>
-    <t>TALITA ARAÚJO BITENCOURT</t>
-  </si>
-  <si>
-    <t>RENATA HOEFTER NIERADKA</t>
-  </si>
-  <si>
     <t>VISION_CONTRATOS</t>
   </si>
   <si>
@@ -488,7 +431,247 @@
     <t>VISION_RESPONSAVEIS</t>
   </si>
   <si>
-    <t>4680008321</t>
+    <t>LT ACESITA - IPATINGA 1</t>
+  </si>
+  <si>
+    <t>LT ÁGUA VERMELHA - SÃO SIMÃO</t>
+  </si>
+  <si>
+    <t>LT AIMORÉS - MASCARENHAS (LT2)</t>
+  </si>
+  <si>
+    <t>LT ARAÇUAÍ 2 - IRAPÉ</t>
+  </si>
+  <si>
+    <t>LT BAGUARI - GOVERNADOR VALADARES 2</t>
+  </si>
+  <si>
+    <t>LT BAGUARI - MESQUITA</t>
+  </si>
+  <si>
+    <t>LT BARÃO DE COCAIS 3 - BRUCUTU</t>
+  </si>
+  <si>
+    <t>LT BARÃO DE COCAIS 3 - JOÃO MONLEVADE 2</t>
+  </si>
+  <si>
+    <t>LT BARÃO DE COCAIS 3 - TAQUARIL</t>
+  </si>
+  <si>
+    <t>LT BARÃO DE COCAIS 3 - WHITE MARTINS/ANGLOGOLD</t>
+  </si>
+  <si>
+    <t>LT BARBACENA 2 - LAFAIETE 1</t>
+  </si>
+  <si>
+    <t>LT BARBACENA 2 - PIMENTA</t>
+  </si>
+  <si>
+    <t>LT BARBACENA 2 - SANTOS DUMONT 2</t>
+  </si>
+  <si>
+    <t>LT BARREIRO - NEVES 1</t>
+  </si>
+  <si>
+    <t>LT BARREIRO - TAQUARIL</t>
+  </si>
+  <si>
+    <t>LT BOM DESPACHO 3 - JAGUARA (LT1)</t>
+  </si>
+  <si>
+    <t>LT BOM DESPACHO 3 - JAGUARA (LT2)</t>
+  </si>
+  <si>
+    <t>LT BOM DESPACHO 3 - NEVES 1 (LT1)</t>
+  </si>
+  <si>
+    <t>LT BOM DESPACHO 3 - NEVES 1 (LT2)</t>
+  </si>
+  <si>
+    <t>LT BOM DESPACHO 3 - SÃO GONÇALO DO PARÁ</t>
+  </si>
+  <si>
+    <t>LT BOM DESPACHO 3 - SÃO GOTARDO 2</t>
+  </si>
+  <si>
+    <t>LT CACHOEIRA PAULISTA - ITAJUBÁ 3</t>
+  </si>
+  <si>
+    <t>LT EMBORCAÇÃO - ITUMBIARA</t>
+  </si>
+  <si>
+    <t>LT EMBORCAÇÃO - NOVA PONTE</t>
+  </si>
+  <si>
+    <t>LT EMBORCAÇÃO - SÃO GOTARDO 2</t>
+  </si>
+  <si>
+    <t>LT FURNAS - PIMENTA (LT2)</t>
+  </si>
+  <si>
+    <t>LT GOVERNADOR VALADARES 6 – GOVERNADOR VALADARES 2</t>
+  </si>
+  <si>
+    <t>LT GOVERNADOR VALADARES 6 – MESQUITA</t>
+  </si>
+  <si>
+    <t>LT GUILMAN AMORIM - IPATINGA 1</t>
+  </si>
+  <si>
+    <t>LT GUILMAN AMORIM - NOVA ERA 2</t>
+  </si>
+  <si>
+    <t>LT IPATINGA 1 - MESQUITA (LT1)</t>
+  </si>
+  <si>
+    <t>LT IPATINGA 1 - MESQUITA (LT2)</t>
+  </si>
+  <si>
+    <t>LT IPATINGA 1 - PORTO ESTRELA</t>
+  </si>
+  <si>
+    <t>LT IPATINGA 1 - USIMINAS</t>
+  </si>
+  <si>
+    <t>LT IRAPÉ - MONTES CLAROS 2</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 2 - ITABIRA 4</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 2 - JOÃO MONLEVADE 2</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 2 - NOVA ERA 2</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 2 - PORTO ESTRELA</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 2 - SABARÁ 3</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 4 - MINA CONCEIÇÃO</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 4 - TAQUARIL</t>
+  </si>
+  <si>
+    <t>LT ITABIRITO 2 - JECEABA</t>
+  </si>
+  <si>
+    <t>LT ITABIRITO 2 - OURO PRETO 2 (LT1)</t>
+  </si>
+  <si>
+    <t>LT ITABIRITO 2 - OURO PRETO 2 (LT2)</t>
+  </si>
+  <si>
+    <t>LT ITABIRITO 2 - SÃO GONÇALO DO PARÁ</t>
+  </si>
+  <si>
+    <t>LT ITABIRITO 2 - VESPASIANO 2</t>
+  </si>
+  <si>
+    <t>LT ITAJUBÁ 3 - POÇOS DE CALDAS</t>
+  </si>
+  <si>
+    <t>LT ITUTINGA - JUIZ DE FORA 1</t>
+  </si>
+  <si>
+    <t>LT JAGUARA - LUIS CARLOS BARRETO (ESTREITO)</t>
+  </si>
+  <si>
+    <t>LT JAGUARA - NOVA PONTE</t>
+  </si>
+  <si>
+    <t>LT JAGUARA - PIMENTA (LT1)</t>
+  </si>
+  <si>
+    <t>LT JAGUARA - PIMENTA (LT2)</t>
+  </si>
+  <si>
+    <t>LT JAGUARA - SÃO SIMÃO</t>
+  </si>
+  <si>
+    <t>LT JAGUARA - VOLTA GRANDE</t>
+  </si>
+  <si>
+    <t>LT JAGUARA 345 KV - JAGUARA 500 KV (LT1)</t>
+  </si>
+  <si>
+    <t>LT JAGUARA 345 KV - JAGUARA 500 KV  (LT2)</t>
+  </si>
+  <si>
+    <t>LT JAGUARA 345 KV - JAGUARA 500 KV  (LT3)</t>
+  </si>
+  <si>
+    <t>LT JECEABA - LAFAIETE 1</t>
+  </si>
+  <si>
+    <t>LT JUIZ DE FORA 1 - SANTOS DUMONT 2</t>
+  </si>
+  <si>
+    <t>LT MESQUITA - USIMINAS</t>
+  </si>
+  <si>
+    <t>LT MESQUITA - VESPASIANO 2</t>
+  </si>
+  <si>
+    <t>LT MONTES CLAROS 2 - VÁRZEA DA PALMA 1</t>
+  </si>
+  <si>
+    <t>LT NEVES 1 - SETE LAGOAS 4</t>
+  </si>
+  <si>
+    <t>LT NEVES 1 - TAQUARIL</t>
+  </si>
+  <si>
+    <t>LT NEVES 1 - VESPASIANO 2</t>
+  </si>
+  <si>
+    <t>LT NOVA ERA 2 - SILICON</t>
+  </si>
+  <si>
+    <t>LT NOVA LIMA 6 - OURO PRETO 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LT NOVA LIMA 6 - TAQUARIL </t>
+  </si>
+  <si>
+    <t>LT PIMENTA - TAQUARIL</t>
+  </si>
+  <si>
+    <t>LT PIRAPORA 2 - VÁRZEA DA PALMA 1</t>
+  </si>
+  <si>
+    <t>LT SABARÁ 3 - TAQUARIL</t>
+  </si>
+  <si>
+    <t>LT SÃO GOTARDO 2 - TRÊS MARIAS</t>
+  </si>
+  <si>
+    <t>LT SETE LAGOAS 4 - TRÊS MARIAS</t>
+  </si>
+  <si>
+    <t>LT TRÊS MARIAS - VÁRZEA DA PALMA 1</t>
+  </si>
+  <si>
+    <t>RS ENGENHARIA</t>
+  </si>
+  <si>
+    <t>RS ENGENHARIA_CONTRATOS</t>
+  </si>
+  <si>
+    <t>RS ENGENHARIA_EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>RS ENGENHARIA_RESPONSAVEIS</t>
+  </si>
+  <si>
+    <t>CLÁUDIA LOPES</t>
+  </si>
+  <si>
+    <t>PACOTE - R&amp;M T LTs 01_2026</t>
   </si>
 </sst>
 </file>
@@ -532,7 +715,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -596,22 +779,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -634,7 +806,12 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -650,6 +827,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -969,10 +1150,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61DBF6C0-D74F-4D47-8600-424F40B056DB}">
-  <dimension ref="A1:AD58"/>
+  <dimension ref="A1:AG132"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="24.5546875" customWidth="1"/>
@@ -981,27 +1162,29 @@
     <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.6640625" customWidth="1"/>
     <col min="9" max="9" width="23.109375" customWidth="1"/>
-    <col min="10" max="10" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="52.21875" customWidth="1"/>
-    <col min="24" max="24" width="29.109375" customWidth="1"/>
-    <col min="25" max="25" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="29.109375" customWidth="1"/>
-    <col min="28" max="30" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.44140625" customWidth="1"/>
+    <col min="11" max="11" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="52.21875" customWidth="1"/>
+    <col min="27" max="27" width="29.109375" customWidth="1"/>
+    <col min="28" max="28" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="29.109375" customWidth="1"/>
+    <col min="31" max="33" width="36.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1009,159 +1192,163 @@
         <v>57</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="J1" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="L1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="S1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="U1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="V1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="W1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="X1" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O1" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="P1" s="7" t="s">
+      <c r="Z1" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="T1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="V1" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="W1" s="7" t="s">
+      <c r="AD1" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="X1" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="Z1" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD1" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>90</v>
-      </c>
+      <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="8" t="s">
-        <v>69</v>
-      </c>
+      <c r="E2" s="8"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="5"/>
+        <v>119</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="11">
+        <v>4680008301</v>
+      </c>
       <c r="K2" s="5"/>
-      <c r="L2" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="8"/>
       <c r="N2" s="5"/>
-      <c r="O2" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="8" t="s">
+      <c r="O2" s="5"/>
+      <c r="P2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB2" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA2" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AC2" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD2" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AG2" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1170,115 +1357,111 @@
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="9" t="s">
-        <v>70</v>
-      </c>
+      <c r="E3" s="9"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
-        <v>148</v>
+      <c r="H3" s="10">
+        <v>4680008321</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="9"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
-      <c r="S3" s="9"/>
+      <c r="S3" s="6"/>
       <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>96</v>
-      </c>
+      <c r="U3" s="9"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
       <c r="AA3" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>103</v>
+        <v>81</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="AD3" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="AE3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF3" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG3" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="8" t="s">
-        <v>71</v>
-      </c>
+      <c r="E4" s="8"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
-      <c r="S4" s="8"/>
+      <c r="S4" s="5"/>
       <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="X4" s="6" t="s">
+      <c r="U4" s="8"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC4" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="Z4" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB4" s="6" t="s">
+      <c r="AD4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE4" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF4" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG4" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AC4" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD4" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -1298,32 +1481,30 @@
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
       <c r="U5" s="6"/>
-      <c r="V5" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="W5" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB5" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC5" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="AD5" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y5" s="6"/>
+      <c r="AC5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF5" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>129</v>
-      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -1343,26 +1524,24 @@
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
-      <c r="V6" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="W6" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AB6" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="AD6" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y6" s="5"/>
+      <c r="AE6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG6" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>61</v>
-      </c>
+      <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -1382,26 +1561,24 @@
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
       <c r="U7" s="6"/>
-      <c r="V7" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="W7" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB7" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD7" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y7" s="6"/>
+      <c r="AE7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG7" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>128</v>
-      </c>
+      <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -1422,76 +1599,75 @@
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
-      <c r="W8" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AB8" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="AD8" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="AE8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG8" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="W9" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB9" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD9" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="AE9" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG9" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB10" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="AD10" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE10" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG10" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AD11" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AG11" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AD12" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AG12" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AD13" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AG13" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -1702,7 +1878,383 @@
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="10"/>
+      <c r="A58" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B132" t="str">
+        <f t="shared" ref="B132" si="0">UPPER(A133)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1710,38 +2262,12 @@
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Classificação: Direcionado</oddFooter>
   </headerFooter>
   <ignoredErrors>
-    <ignoredError sqref="E2:E4 I2 H2" numberStoredAsText="1"/>
+    <ignoredError sqref="H2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Endere_x00e7_o xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Endere_x00e7_o>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002E5C4B65CAC47848AF097160744C818E" ma:contentTypeVersion="21" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="93bce861e0478017e882c2e9311b63ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="f602af69-4847-4411-a4ba-ca5cab174bf1" xmlns:ns3="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d91c369b236210ce7e4ba5a889443938" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2026,27 +2552,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Endere_x00e7_o xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Endere_x00e7_o>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="f602af69-4847-4411-a4ba-ca5cab174bf1"/>
-    <ds:schemaRef ds:uri="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFCD1CA4-4B92-4328-B4B6-8D3186200744}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2066,6 +2598,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="f602af69-4847-4411-a4ba-ca5cab174bf1"/>
+    <ds:schemaRef ds:uri="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{723fd9ce-6d6d-415e-88a7-385d6d41dc16}" enabled="1" method="Privileged" siteId="{97ce2340-9c1d-45b1-a835-7ea811b6fe9a}" removed="0"/>

--- a/BASE INTERNA.xlsx
+++ b/BASE INTERNA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cemigbr.sharepoint.com/sites/eoet_equipamentos/Documentos Compartilhados/TRAMITAÇÃO DE DOCUMENTOS/SCRIPT PYTHON/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="8_{71FA6A9E-4B71-4B0B-AE43-8B20072134D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04CA4233-D7DD-44E2-BFE6-42DFE2472EF7}"/>
+  <xr:revisionPtr revIDLastSave="305" documentId="8_{71FA6A9E-4B71-4B0B-AE43-8B20072134D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D163EC3-021C-4481-8B0B-97F7134D3E7F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B330CE1A-85B8-4702-A854-85C1BDD9E2C6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Base" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$Y$1:$Y$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$H$1:$H$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="211">
   <si>
     <t>SUBESTACAO</t>
   </si>
@@ -401,9 +401,6 @@
     <t>RODRIGO SERPA FERREIRA PASSOS</t>
   </si>
   <si>
-    <t>4680008320</t>
-  </si>
-  <si>
     <t>MARCO TÚLIO SOUZA</t>
   </si>
   <si>
@@ -672,13 +669,19 @@
   </si>
   <si>
     <t>PACOTE - R&amp;M T LTs 01_2026</t>
+  </si>
+  <si>
+    <t>PACOTE - R&amp;M 02_2023</t>
+  </si>
+  <si>
+    <t>PACOTE - R&amp;M 01_2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -690,6 +693,12 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -783,7 +792,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -810,6 +819,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1207,13 +1222,13 @@
         <v>63</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>64</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>65</v>
@@ -1231,13 +1246,13 @@
         <v>70</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>71</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>72</v>
@@ -1255,13 +1270,13 @@
         <v>76</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y1" s="7" t="s">
         <v>77</v>
       </c>
       <c r="Z1" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AA1" s="7" t="s">
         <v>78</v>
@@ -1295,8 +1310,8 @@
       <c r="E2" s="8"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
-        <v>119</v>
+      <c r="H2" s="12">
+        <v>4680007951</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="11">
@@ -1308,11 +1323,11 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5" t="s">
-        <v>67</v>
+        <v>209</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S2" s="5"/>
       <c r="T2" s="5"/>
@@ -1320,11 +1335,11 @@
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
       <c r="X2" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y2" s="5"/>
       <c r="Z2" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AA2" s="5" t="s">
         <v>79</v>
@@ -1370,7 +1385,9 @@
       <c r="M3" s="9"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
+      <c r="P3" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
@@ -1379,7 +1396,7 @@
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
       <c r="X3" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
@@ -1410,14 +1427,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="8"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="12">
+        <v>4680004845</v>
+      </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -1425,7 +1444,9 @@
       <c r="M4" s="8"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="P4" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
@@ -1434,7 +1455,7 @@
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
       <c r="X4" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
@@ -1450,7 +1471,7 @@
       <c r="AE4" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AF4" s="5" t="s">
         <v>117</v>
       </c>
       <c r="AG4" s="6" t="s">
@@ -1467,7 +1488,9 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
+      <c r="H5" s="13">
+        <v>4680007844</v>
+      </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
@@ -1484,7 +1507,7 @@
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
       <c r="X5" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Y5" s="6"/>
       <c r="AC5" s="6" t="s">
@@ -1493,7 +1516,7 @@
       <c r="AE5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="AF5" s="5" t="s">
+      <c r="AF5" s="6" t="s">
         <v>118</v>
       </c>
       <c r="AG5" s="5" t="s">
@@ -1510,7 +1533,9 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="H6" s="12">
+        <v>4680008320</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -1527,11 +1552,14 @@
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
       <c r="X6" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y6" s="5"/>
       <c r="AE6" s="5" t="s">
         <v>96</v>
+      </c>
+      <c r="AF6" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="AG6" s="6" t="s">
         <v>106</v>
@@ -1564,11 +1592,14 @@
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
       <c r="X7" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y7" s="6"/>
       <c r="AE7" s="6" t="s">
         <v>97</v>
+      </c>
+      <c r="AF7" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="AG7" s="5" t="s">
         <v>105</v>
@@ -1879,377 +1910,377 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132" si="0">UPPER(A133)</f>
@@ -2257,17 +2288,41 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Classificação: Direcionado</oddFooter>
   </headerFooter>
-  <ignoredErrors>
-    <ignoredError sqref="H2" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Endere_x00e7_o xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Endere_x00e7_o>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002E5C4B65CAC47848AF097160744C818E" ma:contentTypeVersion="21" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="93bce861e0478017e882c2e9311b63ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="f602af69-4847-4411-a4ba-ca5cab174bf1" xmlns:ns3="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d91c369b236210ce7e4ba5a889443938" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2552,33 +2607,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Endere_x00e7_o xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Endere_x00e7_o>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="f602af69-4847-4411-a4ba-ca5cab174bf1"/>
+    <ds:schemaRef ds:uri="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFCD1CA4-4B92-4328-B4B6-8D3186200744}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2598,26 +2647,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="f602af69-4847-4411-a4ba-ca5cab174bf1"/>
-    <ds:schemaRef ds:uri="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{723fd9ce-6d6d-415e-88a7-385d6d41dc16}" enabled="1" method="Privileged" siteId="{97ce2340-9c1d-45b1-a835-7ea811b6fe9a}" removed="0"/>

--- a/BASE INTERNA.xlsx
+++ b/BASE INTERNA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cemigbr.sharepoint.com/sites/eoet_equipamentos/Documentos Compartilhados/TRAMITAÇÃO DE DOCUMENTOS/SCRIPT PYTHON/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="305" documentId="8_{71FA6A9E-4B71-4B0B-AE43-8B20072134D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D163EC3-021C-4481-8B0B-97F7134D3E7F}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="8_{71FA6A9E-4B71-4B0B-AE43-8B20072134D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55F45871-F1C6-41F5-9330-D4E87107E415}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B330CE1A-85B8-4702-A854-85C1BDD9E2C6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B330CE1A-85B8-4702-A854-85C1BDD9E2C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -792,7 +792,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -815,16 +815,10 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1310,11 +1304,11 @@
       <c r="E2" s="8"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
-      <c r="H2" s="12">
-        <v>4680007951</v>
+      <c r="H2" s="5">
+        <v>4680004845</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="11">
+      <c r="J2" s="10">
         <v>4680008301</v>
       </c>
       <c r="K2" s="5"/>
@@ -1375,8 +1369,8 @@
       <c r="E3" s="9"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="10">
-        <v>4680008321</v>
+      <c r="H3" s="6">
+        <v>4680007844</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
@@ -1434,8 +1428,8 @@
       <c r="E4" s="8"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="12">
-        <v>4680004845</v>
+      <c r="H4" s="5">
+        <v>4680007951</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -1488,8 +1482,8 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="13">
-        <v>4680007844</v>
+      <c r="H5" s="6">
+        <v>4680008320</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -1533,8 +1527,8 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="12">
-        <v>4680008320</v>
+      <c r="H6" s="11">
+        <v>4680008321</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -2314,15 +2308,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002E5C4B65CAC47848AF097160744C818E" ma:contentTypeVersion="21" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="93bce861e0478017e882c2e9311b63ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="f602af69-4847-4411-a4ba-ca5cab174bf1" xmlns:ns3="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d91c369b236210ce7e4ba5a889443938" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2607,6 +2592,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
   <ds:schemaRefs>
@@ -2620,14 +2614,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFCD1CA4-4B92-4328-B4B6-8D3186200744}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2647,6 +2633,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{723fd9ce-6d6d-415e-88a7-385d6d41dc16}" enabled="1" method="Privileged" siteId="{97ce2340-9c1d-45b1-a835-7ea811b6fe9a}" removed="0"/>

--- a/BASE INTERNA.xlsx
+++ b/BASE INTERNA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cemigbr.sharepoint.com/sites/eoet_equipamentos/Documentos Compartilhados/TRAMITAÇÃO DE DOCUMENTOS/SCRIPT PYTHON/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c055483\CEMIG\EI ET - Equipamentos - Documentos\TRAMITAÇÃO DE DOCUMENTOS\SCRIPT PYTHON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="8_{71FA6A9E-4B71-4B0B-AE43-8B20072134D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55F45871-F1C6-41F5-9330-D4E87107E415}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C53866-0C78-47E5-92FE-2F1B6D6C615E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B330CE1A-85B8-4702-A854-85C1BDD9E2C6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="230">
   <si>
     <t>SUBESTACAO</t>
   </si>
@@ -675,6 +675,63 @@
   </si>
   <si>
     <t>PACOTE - R&amp;M 01_2024</t>
+  </si>
+  <si>
+    <t>LT BARREIRO - BETIM 6</t>
+  </si>
+  <si>
+    <t>LT BETIM 6 - NEVES 1</t>
+  </si>
+  <si>
+    <t>LT IPATINGA 1 - MESQUITA</t>
+  </si>
+  <si>
+    <t>LT MESQUITA - PORTO ESTRELA</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 2 - ITABIRA 5</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 4 - ITABIRA 5</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 2 - JOÃO MONLEVADE 4</t>
+  </si>
+  <si>
+    <t>LT JOÃO MONLEVADE 2 - JOÃO MONLEVADE 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LT BRAÚNAS - ITABIRA 2 </t>
+  </si>
+  <si>
+    <t>LT BRAÚNAS - PORTO ESTRELA</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 5 - SABARÁ 3</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 5 - MESQUITA</t>
+  </si>
+  <si>
+    <t>LT ITABIRA 5 - VESPASIANO 2</t>
+  </si>
+  <si>
+    <t>LT PIRAPORA 2 - VÁRZEA DA PALMA 4</t>
+  </si>
+  <si>
+    <t>LT VÁRZEA DA PALMA 1 - VÁRZEA DA PALMA 4</t>
+  </si>
+  <si>
+    <t>LT VÁRZEA DA PALMA 4 - PIRAPORA 2</t>
+  </si>
+  <si>
+    <t>LT BURITIZEIRO 3 - VÁRZEA DA PALMA 4</t>
+  </si>
+  <si>
+    <t>LT BURITIZEIRO 3 - VÁRZEA DA PALMA 1</t>
+  </si>
+  <si>
+    <t>LTs DIVERSAS</t>
   </si>
 </sst>
 </file>
@@ -724,7 +781,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -788,11 +845,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -818,8 +890,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -836,10 +917,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1159,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61DBF6C0-D74F-4D47-8600-424F40B056DB}">
-  <dimension ref="A1:AG132"/>
+  <dimension ref="A1:AG152"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.88671875" bestFit="1" customWidth="1"/>
@@ -1527,7 +1604,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="11">
+      <c r="H6" s="10">
         <v>4680008321</v>
       </c>
       <c r="I6" s="5"/>
@@ -1904,381 +1981,477 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="12" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="12" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="12" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="12" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="12" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="11" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="11" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="12" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="11" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="12" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="12" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="11" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="12" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="11" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="11" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="11" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="12" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="11" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="12" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="11" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="12" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="11" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="12" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="11" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="12" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="11" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="12" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="11" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="12" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="11" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="12" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="11" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" s="12" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" s="11" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" s="12" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" s="11" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" s="12" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" s="11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" s="12" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" s="11" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="11" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="12" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="1" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" s="11" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" s="12" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" s="1" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" s="11" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" s="12" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" s="1" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" s="11" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" s="12" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" s="11" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" s="12" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" s="1" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" s="11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" s="12" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="3" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" s="11" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="12" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="11" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="11" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="11" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="12" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="1" t="s">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="11" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="12" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="1" t="s">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="11" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" s="12" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="1" t="s">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" s="11" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" s="12" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="1" t="s">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" s="11" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" s="12" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="1" t="s">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="11" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="11" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A130" s="1" t="s">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="12" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="11" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A132" s="1" t="s">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B132" t="str">
-        <f t="shared" ref="B132" si="0">UPPER(A133)</f>
-        <v/>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" s="14" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -2291,20 +2464,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Endere_x00e7_o xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Endere_x00e7_o>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2593,22 +2758,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Endere_x00e7_o xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Endere_x00e7_o>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="f602af69-4847-4411-a4ba-ca5cab174bf1"/>
-    <ds:schemaRef ds:uri="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2634,9 +2803,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="f602af69-4847-4411-a4ba-ca5cab174bf1"/>
+    <ds:schemaRef ds:uri="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/BASE INTERNA.xlsx
+++ b/BASE INTERNA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c055483\CEMIG\EI ET - Equipamentos - Documentos\TRAMITAÇÃO DE DOCUMENTOS\SCRIPT PYTHON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cemigbr.sharepoint.com/sites/eoet_equipamentos/Documentos Compartilhados/TRAMITAÇÃO DE DOCUMENTOS/SCRIPT PYTHON/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C53866-0C78-47E5-92FE-2F1B6D6C615E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{13C53866-0C78-47E5-92FE-2F1B6D6C615E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67708F7D-1B47-4776-825C-96E43554412F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B330CE1A-85B8-4702-A854-85C1BDD9E2C6}"/>
+    <workbookView xWindow="28680" yWindow="1605" windowWidth="29040" windowHeight="15720" xr2:uid="{B330CE1A-85B8-4702-A854-85C1BDD9E2C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -557,12 +557,6 @@
     <t>LT ITABIRITO 2 - JECEABA</t>
   </si>
   <si>
-    <t>LT ITABIRITO 2 - OURO PRETO 2 (LT1)</t>
-  </si>
-  <si>
-    <t>LT ITABIRITO 2 - OURO PRETO 2 (LT2)</t>
-  </si>
-  <si>
     <t>LT ITABIRITO 2 - SÃO GONÇALO DO PARÁ</t>
   </si>
   <si>
@@ -732,6 +726,12 @@
   </si>
   <si>
     <t>LTs DIVERSAS</t>
+  </si>
+  <si>
+    <t>LT ITABIRITO 2 - OURO PRETO 2 (345 kV)</t>
+  </si>
+  <si>
+    <t>LT ITABIRITO 2 - OURO PRETO 2 (500 kV)</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1299,7 @@
         <v>64</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>65</v>
@@ -1323,7 +1323,7 @@
         <v>71</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>72</v>
@@ -1347,7 +1347,7 @@
         <v>77</v>
       </c>
       <c r="Z1" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AA1" s="7" t="s">
         <v>78</v>
@@ -1394,11 +1394,11 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="S2" s="5"/>
       <c r="T2" s="5"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Y2" s="5"/>
       <c r="Z2" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AA2" s="5" t="s">
         <v>79</v>
@@ -1457,7 +1457,7 @@
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
@@ -1498,7 +1498,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
@@ -2051,7 +2051,7 @@
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
@@ -2101,22 +2101,22 @@
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
@@ -2166,7 +2166,7 @@
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
@@ -2201,12 +2201,12 @@
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
@@ -2216,7 +2216,7 @@
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
@@ -2236,7 +2236,7 @@
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
@@ -2251,17 +2251,17 @@
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
@@ -2271,187 +2271,187 @@
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="11" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="11" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2473,6 +2473,23 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Endere_x00e7_o xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Endere_x00e7_o>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002E5C4B65CAC47848AF097160744C818E" ma:contentTypeVersion="21" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="93bce861e0478017e882c2e9311b63ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="f602af69-4847-4411-a4ba-ca5cab174bf1" xmlns:ns3="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d91c369b236210ce7e4ba5a889443938" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2757,23 +2774,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Endere_x00e7_o xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Endere_x00e7_o>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
   <ds:schemaRefs>
@@ -2783,6 +2783,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="f602af69-4847-4411-a4ba-ca5cab174bf1"/>
+    <ds:schemaRef ds:uri="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFCD1CA4-4B92-4328-B4B6-8D3186200744}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2802,18 +2814,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="f602af69-4847-4411-a4ba-ca5cab174bf1"/>
-    <ds:schemaRef ds:uri="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{723fd9ce-6d6d-415e-88a7-385d6d41dc16}" enabled="1" method="Privileged" siteId="{97ce2340-9c1d-45b1-a835-7ea811b6fe9a}" removed="0"/>

--- a/BASE INTERNA.xlsx
+++ b/BASE INTERNA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cemigbr.sharepoint.com/sites/eoet_equipamentos/Documentos Compartilhados/TRAMITAÇÃO DE DOCUMENTOS/SCRIPT PYTHON/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{13C53866-0C78-47E5-92FE-2F1B6D6C615E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67708F7D-1B47-4776-825C-96E43554412F}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{13C53866-0C78-47E5-92FE-2F1B6D6C615E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62ADD637-0AF4-4A88-AAE5-9E0EA73083FA}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1605" windowWidth="29040" windowHeight="15720" xr2:uid="{B330CE1A-85B8-4702-A854-85C1BDD9E2C6}"/>
+    <workbookView xWindow="-19320" yWindow="2565" windowWidth="19440" windowHeight="14880" xr2:uid="{B330CE1A-85B8-4702-A854-85C1BDD9E2C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="231">
   <si>
     <t>SUBESTACAO</t>
   </si>
@@ -732,6 +732,9 @@
   </si>
   <si>
     <t>LT ITABIRITO 2 - OURO PRETO 2 (500 kV)</t>
+  </si>
+  <si>
+    <t>CAMILE ARAUJO</t>
   </si>
 </sst>
 </file>
@@ -917,6 +920,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1526,7 +1533,7 @@
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
       <c r="X4" s="5" t="s">
-        <v>122</v>
+        <v>230</v>
       </c>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
@@ -1578,7 +1585,7 @@
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
       <c r="X5" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Y5" s="6"/>
       <c r="AC5" s="6" t="s">
@@ -1623,7 +1630,7 @@
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
       <c r="X6" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Y6" s="5"/>
       <c r="AE6" s="5" t="s">
@@ -1663,7 +1670,7 @@
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
       <c r="X7" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Y7" s="6"/>
       <c r="AE7" s="6" t="s">
@@ -1702,7 +1709,9 @@
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
+      <c r="X8" s="5" t="s">
+        <v>123</v>
+      </c>
       <c r="Y8" s="5"/>
       <c r="AE8" s="5" t="s">
         <v>98</v>
@@ -2464,32 +2473,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Endere_x00e7_o xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Endere_x00e7_o>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002E5C4B65CAC47848AF097160744C818E" ma:contentTypeVersion="21" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="93bce861e0478017e882c2e9311b63ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="f602af69-4847-4411-a4ba-ca5cab174bf1" xmlns:ns3="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d91c369b236210ce7e4ba5a889443938" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2774,27 +2757,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Endere_x00e7_o xmlns="f602af69-4847-4411-a4ba-ca5cab174bf1">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Endere_x00e7_o>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="f602af69-4847-4411-a4ba-ca5cab174bf1"/>
-    <ds:schemaRef ds:uri="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFCD1CA4-4B92-4328-B4B6-8D3186200744}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2814,6 +2803,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B557BF0-D109-4AAF-A278-461EA218ABE3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="f602af69-4847-4411-a4ba-ca5cab174bf1"/>
+    <ds:schemaRef ds:uri="ee2c174e-7a73-4a5a-ba1f-9194dbdc55b0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C0514-5F18-4567-AAC0-AF8A16E7FB2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{723fd9ce-6d6d-415e-88a7-385d6d41dc16}" enabled="1" method="Privileged" siteId="{97ce2340-9c1d-45b1-a835-7ea811b6fe9a}" removed="0"/>
